--- a/static/files/template_riesgos.xlsx
+++ b/static/files/template_riesgos.xlsx
@@ -2685,161 +2685,212 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" style="19" min="1" max="1"/>
-    <col width="30" customWidth="1" style="19" min="2" max="2"/>
+    <col width="38" customWidth="1" style="19" min="1" max="1"/>
+    <col width="28" customWidth="1" style="19" min="2" max="2"/>
     <col width="92" customWidth="1" style="19" min="3" max="3"/>
+    <col width="10" customWidth="1" style="19" min="4" max="4"/>
+    <col width="10" customWidth="1" style="19" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" s="19">
-      <c r="A1" s="24" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>Relación con fases del cronograma</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="19">
-      <c r="A2" s="16" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>Fase del cronograma</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="27" t="inlineStr">
         <is>
           <t>Riesgos más relevantes</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="27" t="inlineStr">
         <is>
           <t>Acciones de control</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="D2" s="27" t="inlineStr">
+        <is>
+          <t>Inicio</t>
+        </is>
+      </c>
+      <c r="E2" s="27" t="inlineStr">
+        <is>
+          <t>Fin</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1" s="19">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>Inicio y planificación</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>R01, R02, R03, R04, R05, R22</t>
         </is>
       </c>
-      <c r="C3" s="17" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t>Aprobar Project Charter, definir alcance, elaborar cronograma, matriz de recursos y control de cambios.</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="28.5" customHeight="1" s="19">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="D3" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1" s="19">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>Levantamiento y comprensión del negocio</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>R06, R07, R08</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="28" t="inlineStr">
         <is>
           <t>Sesiones con Product Owner, validación de procesos contables y criterios documentales.</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="D4" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="28" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1" s="19">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>Datos, OCR y Data Mining</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>R09, R10, R12, R13, R14</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>Recolección mínima por categoría, limpieza, etiquetado, pruebas OCR y validación de dataset.</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="D5" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="28" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1" s="19">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>Modelado IA</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>R15, R16, R17</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>Comparación de modelos, evaluación con métricas ML, ajuste y reentrenamiento.</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="D6" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" s="28" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1" s="19">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>Desarrollo web y base de datos</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>R18, R19, R20, R21, R23</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t>Contratos API, revisión de arquitectura, controles de acceso, pruebas unitarias e integración.</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="D7" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" s="28" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1" s="19">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>Pruebas y validación</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>R24, R25</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>Plan QA, pruebas de API, pruebas funcionales, UAT y actas de aceptación.</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="D8" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" s="28" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1" s="19">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>Despliegue, capacitación y cierre</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="28" t="inlineStr">
         <is>
           <t>R26, R27, R28, R29, R30</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t>Despliegue controlado, monitoreo, manuales, capacitación, transferencia y cierre formal.</t>
         </is>
       </c>
+      <c r="D9" s="28" t="n">
+        <v>11</v>
+      </c>
+      <c r="E9" s="28" t="n">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
